--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_8CCDB92F30ECE959B60F0320098CDF696F824052" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16048D19-76B9-48E9-A83E-F2C8F8364641}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="11_8CCDB92F30ECE959B60F0320098CDF696F824052" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5BD266F-E47C-56F0-9F9A-1C052292E441}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39619,7 +39619,7 @@
       </c>
       <c r="R554" s="4"/>
       <c r="S554" s="4">
-        <f t="shared" ref="S554:S590" si="1">+A554</f>
+        <f t="shared" ref="S554:S589" si="1">+A554</f>
         <v>478</v>
       </c>
       <c r="T554" s="4">

--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="11_8CCDB92F30ECE959B60F0320098CDF696F824052" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5BD266F-E47C-56F0-9F9A-1C052292E441}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="11_8CCDB92F30ECE959B60F0320098CDF696F824052" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C784ECFC-FB97-4B98-BEAC-6291396D773D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -45761,7 +45761,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W661" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="215" priority="115"/>
   </conditionalFormatting>
